--- a/BVSimulationFiles/82.xlsx
+++ b/BVSimulationFiles/82.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -483,64 +483,64 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0005339805825242719</v>
+        <v>0.001067961165048544</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0005485749055083913</v>
+        <v>0.001097149811016783</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0005630399836086849</v>
+        <v>0.00112607996721737</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0005773766337588696</v>
+        <v>0.001154753267517739</v>
       </c>
       <c r="F2" t="n">
-        <v>0.000591585668356275</v>
+        <v>0.00118317133671255</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0006056678952853533</v>
+        <v>0.001211335790570707</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0006196241179410693</v>
+        <v>0.001239248235882139</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0006334551352521747</v>
+        <v>0.001266910270504349</v>
       </c>
       <c r="J2" t="n">
-        <v>0.000647161741704368</v>
+        <v>0.001294323483408736</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0006607447273633384</v>
+        <v>0.001321489454726677</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0006742048778976952</v>
+        <v>0.00134840975579539</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0006875429746017839</v>
+        <v>0.001375085949203568</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0007007597944183896</v>
+        <v>0.001401519588836779</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0007138561099613252</v>
+        <v>0.00142771221992265</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0007268326895379096</v>
+        <v>0.001453665379075819</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.000739690297171333</v>
+        <v>0.001479380594342666</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0007524296926229131</v>
+        <v>0.001504859385245826</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0007650516314142364</v>
+        <v>0.001530103262828473</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0007775568648491944</v>
+        <v>0.001555113729698389</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0007899461400359066</v>
+        <v>0.001579892280071813</v>
       </c>
     </row>
     <row r="3">
@@ -548,64 +548,64 @@
         <v>0.955</v>
       </c>
       <c r="B3" t="n">
-        <v>0.0005339805825242719</v>
+        <v>0.001067961165048544</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0005485749055083913</v>
+        <v>0.001097149811016783</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0005630399836086849</v>
+        <v>0.00112607996721737</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0005773766337588696</v>
+        <v>0.001154753267517739</v>
       </c>
       <c r="F3" t="n">
-        <v>0.000591585668356275</v>
+        <v>0.00118317133671255</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0006056678952853533</v>
+        <v>0.001211335790570707</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0006196241179410693</v>
+        <v>0.001239248235882139</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0006334551352521747</v>
+        <v>0.001266910270504349</v>
       </c>
       <c r="J3" t="n">
-        <v>0.000647161741704368</v>
+        <v>0.001294323483408736</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0006607447273633384</v>
+        <v>0.001321489454726677</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0006742048778976952</v>
+        <v>0.00134840975579539</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0006875429746017839</v>
+        <v>0.001375085949203568</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0007007597944183896</v>
+        <v>0.001401519588836779</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0007138561099613252</v>
+        <v>0.00142771221992265</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0007268326895379096</v>
+        <v>0.001453665379075819</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.000739690297171333</v>
+        <v>0.001479380594342666</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0007524296926229131</v>
+        <v>0.001504859385245826</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0007650516314142364</v>
+        <v>0.001530103262828473</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0007775568648491944</v>
+        <v>0.001555113729698389</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0007899461400359066</v>
+        <v>0.001579892280071813</v>
       </c>
     </row>
   </sheetData>

--- a/BVSimulationFiles/82.xlsx
+++ b/BVSimulationFiles/82.xlsx
@@ -483,64 +483,64 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.001067961165048544</v>
+        <v>0.01067961165048544</v>
       </c>
       <c r="C2" t="n">
-        <v>0.001097149811016783</v>
+        <v>0.01097149811016783</v>
       </c>
       <c r="D2" t="n">
-        <v>0.00112607996721737</v>
+        <v>0.0112607996721737</v>
       </c>
       <c r="E2" t="n">
-        <v>0.001154753267517739</v>
+        <v>0.01154753267517739</v>
       </c>
       <c r="F2" t="n">
-        <v>0.00118317133671255</v>
+        <v>0.0118317133671255</v>
       </c>
       <c r="G2" t="n">
-        <v>0.001211335790570707</v>
+        <v>0.01211335790570707</v>
       </c>
       <c r="H2" t="n">
-        <v>0.001239248235882139</v>
+        <v>0.01239248235882139</v>
       </c>
       <c r="I2" t="n">
-        <v>0.001266910270504349</v>
+        <v>0.01266910270504349</v>
       </c>
       <c r="J2" t="n">
-        <v>0.001294323483408736</v>
+        <v>0.01294323483408736</v>
       </c>
       <c r="K2" t="n">
-        <v>0.001321489454726677</v>
+        <v>0.01321489454726677</v>
       </c>
       <c r="L2" t="n">
-        <v>0.00134840975579539</v>
+        <v>0.0134840975579539</v>
       </c>
       <c r="M2" t="n">
-        <v>0.001375085949203568</v>
+        <v>0.01375085949203568</v>
       </c>
       <c r="N2" t="n">
-        <v>0.001401519588836779</v>
+        <v>0.01401519588836779</v>
       </c>
       <c r="O2" t="n">
-        <v>0.00142771221992265</v>
+        <v>0.0142771221992265</v>
       </c>
       <c r="P2" t="n">
-        <v>0.001453665379075819</v>
+        <v>0.01453665379075819</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.001479380594342666</v>
+        <v>0.01479380594342666</v>
       </c>
       <c r="R2" t="n">
-        <v>0.001504859385245826</v>
+        <v>0.01504859385245826</v>
       </c>
       <c r="S2" t="n">
-        <v>0.001530103262828473</v>
+        <v>0.01530103262828473</v>
       </c>
       <c r="T2" t="n">
-        <v>0.001555113729698389</v>
+        <v>0.01555113729698389</v>
       </c>
       <c r="U2" t="n">
-        <v>0.001579892280071813</v>
+        <v>0.01579892280071813</v>
       </c>
     </row>
     <row r="3">
@@ -548,64 +548,64 @@
         <v>0.955</v>
       </c>
       <c r="B3" t="n">
-        <v>0.001067961165048544</v>
+        <v>0.01067961165048544</v>
       </c>
       <c r="C3" t="n">
-        <v>0.001097149811016783</v>
+        <v>0.01097149811016783</v>
       </c>
       <c r="D3" t="n">
-        <v>0.00112607996721737</v>
+        <v>0.0112607996721737</v>
       </c>
       <c r="E3" t="n">
-        <v>0.001154753267517739</v>
+        <v>0.01154753267517739</v>
       </c>
       <c r="F3" t="n">
-        <v>0.00118317133671255</v>
+        <v>0.0118317133671255</v>
       </c>
       <c r="G3" t="n">
-        <v>0.001211335790570707</v>
+        <v>0.01211335790570707</v>
       </c>
       <c r="H3" t="n">
-        <v>0.001239248235882139</v>
+        <v>0.01239248235882139</v>
       </c>
       <c r="I3" t="n">
-        <v>0.001266910270504349</v>
+        <v>0.01266910270504349</v>
       </c>
       <c r="J3" t="n">
-        <v>0.001294323483408736</v>
+        <v>0.01294323483408736</v>
       </c>
       <c r="K3" t="n">
-        <v>0.001321489454726677</v>
+        <v>0.01321489454726677</v>
       </c>
       <c r="L3" t="n">
-        <v>0.00134840975579539</v>
+        <v>0.0134840975579539</v>
       </c>
       <c r="M3" t="n">
-        <v>0.001375085949203568</v>
+        <v>0.01375085949203568</v>
       </c>
       <c r="N3" t="n">
-        <v>0.001401519588836779</v>
+        <v>0.01401519588836779</v>
       </c>
       <c r="O3" t="n">
-        <v>0.00142771221992265</v>
+        <v>0.0142771221992265</v>
       </c>
       <c r="P3" t="n">
-        <v>0.001453665379075819</v>
+        <v>0.01453665379075819</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.001479380594342666</v>
+        <v>0.01479380594342666</v>
       </c>
       <c r="R3" t="n">
-        <v>0.001504859385245826</v>
+        <v>0.01504859385245826</v>
       </c>
       <c r="S3" t="n">
-        <v>0.001530103262828473</v>
+        <v>0.01530103262828473</v>
       </c>
       <c r="T3" t="n">
-        <v>0.001555113729698389</v>
+        <v>0.01555113729698389</v>
       </c>
       <c r="U3" t="n">
-        <v>0.001579892280071813</v>
+        <v>0.01579892280071813</v>
       </c>
     </row>
   </sheetData>

--- a/BVSimulationFiles/82.xlsx
+++ b/BVSimulationFiles/82.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U3"/>
+  <dimension ref="A1:AE3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -421,60 +421,90 @@
         <v>0</v>
       </c>
       <c r="C1" t="n">
-        <v>0.00882578947368421</v>
+        <v>0.005782413793103448</v>
       </c>
       <c r="D1" t="n">
-        <v>0.01765157894736842</v>
+        <v>0.0115648275862069</v>
       </c>
       <c r="E1" t="n">
-        <v>0.02647736842105263</v>
+        <v>0.01734724137931035</v>
       </c>
       <c r="F1" t="n">
-        <v>0.03530315789473684</v>
+        <v>0.02312965517241379</v>
       </c>
       <c r="G1" t="n">
-        <v>0.04412894736842105</v>
+        <v>0.02891206896551724</v>
       </c>
       <c r="H1" t="n">
-        <v>0.05295473684210526</v>
+        <v>0.03469448275862069</v>
       </c>
       <c r="I1" t="n">
-        <v>0.06178052631578947</v>
+        <v>0.04047689655172413</v>
       </c>
       <c r="J1" t="n">
-        <v>0.07060631578947368</v>
+        <v>0.04625931034482758</v>
       </c>
       <c r="K1" t="n">
-        <v>0.07943210526315789</v>
+        <v>0.05204172413793104</v>
       </c>
       <c r="L1" t="n">
-        <v>0.0882578947368421</v>
+        <v>0.05782413793103448</v>
       </c>
       <c r="M1" t="n">
-        <v>0.09708368421052631</v>
+        <v>0.06360655172413793</v>
       </c>
       <c r="N1" t="n">
-        <v>0.1059094736842105</v>
+        <v>0.06938896551724139</v>
       </c>
       <c r="O1" t="n">
-        <v>0.1147352631578947</v>
+        <v>0.07517137931034483</v>
       </c>
       <c r="P1" t="n">
-        <v>0.1235610526315789</v>
+        <v>0.08095379310344826</v>
       </c>
       <c r="Q1" t="n">
-        <v>0.1323868421052632</v>
+        <v>0.08673620689655172</v>
       </c>
       <c r="R1" t="n">
-        <v>0.1412126315789474</v>
+        <v>0.09251862068965516</v>
       </c>
       <c r="S1" t="n">
-        <v>0.1500384210526316</v>
+        <v>0.09830103448275862</v>
       </c>
       <c r="T1" t="n">
-        <v>0.1588642105263158</v>
+        <v>0.1040834482758621</v>
       </c>
       <c r="U1" t="n">
+        <v>0.1098658620689655</v>
+      </c>
+      <c r="V1" t="n">
+        <v>0.115648275862069</v>
+      </c>
+      <c r="W1" t="n">
+        <v>0.1214306896551724</v>
+      </c>
+      <c r="X1" t="n">
+        <v>0.1272131034482759</v>
+      </c>
+      <c r="Y1" t="n">
+        <v>0.1329955172413793</v>
+      </c>
+      <c r="Z1" t="n">
+        <v>0.1387779310344828</v>
+      </c>
+      <c r="AA1" t="n">
+        <v>0.1445603448275862</v>
+      </c>
+      <c r="AB1" t="n">
+        <v>0.1503427586206897</v>
+      </c>
+      <c r="AC1" t="n">
+        <v>0.1561251724137931</v>
+      </c>
+      <c r="AD1" t="n">
+        <v>0.1619075862068965</v>
+      </c>
+      <c r="AE1" t="n">
         <v>0.16769</v>
       </c>
     </row>
@@ -483,64 +513,94 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01067961165048544</v>
+        <v>0.03300413562090393</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01097149811016783</v>
+        <v>0.03350533315393842</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0112607996721737</v>
+        <v>0.03400016596126504</v>
       </c>
       <c r="E2" t="n">
-        <v>0.01154753267517739</v>
+        <v>0.03448868810984104</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0118317133671255</v>
+        <v>0.03497095326860401</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01211335790570707</v>
+        <v>0.03544701471119215</v>
       </c>
       <c r="H2" t="n">
-        <v>0.01239248235882139</v>
+        <v>0.03591692531864685</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01266910270504349</v>
+        <v>0.03638073758209763</v>
       </c>
       <c r="J2" t="n">
-        <v>0.01294323483408736</v>
+        <v>0.03683850360542971</v>
       </c>
       <c r="K2" t="n">
-        <v>0.01321489454726677</v>
+        <v>0.03729027510793367</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0134840975579539</v>
+        <v>0.03773610342693843</v>
       </c>
       <c r="M2" t="n">
-        <v>0.01375085949203568</v>
+        <v>0.03817603952042645</v>
       </c>
       <c r="N2" t="n">
-        <v>0.01401519588836779</v>
+        <v>0.03861013396963224</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0142771221992265</v>
+        <v>0.03903843698162362</v>
       </c>
       <c r="P2" t="n">
-        <v>0.01453665379075819</v>
+        <v>0.03946099839186622</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.01479380594342666</v>
+        <v>0.03987786766677121</v>
       </c>
       <c r="R2" t="n">
-        <v>0.01504859385245826</v>
+        <v>0.04028909390622624</v>
       </c>
       <c r="S2" t="n">
-        <v>0.01530103262828473</v>
+        <v>0.04069472584611</v>
       </c>
       <c r="T2" t="n">
-        <v>0.01555113729698389</v>
+        <v>0.04109481186079007</v>
       </c>
       <c r="U2" t="n">
-        <v>0.01579892280071813</v>
+        <v>0.0414893999656048</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.04187853781932839</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0.04226227272662041</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0.04264065164045885</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0.04301372116455741</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0.04338152755576688</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0.04374411672646084</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.04410153424690568</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0.04445382534761502</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0.04480103492168887</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0.04514320752713721</v>
       </c>
     </row>
     <row r="3">
@@ -548,64 +608,94 @@
         <v>0.955</v>
       </c>
       <c r="B3" t="n">
-        <v>0.01067961165048544</v>
+        <v>0.03300413562090393</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01097149811016783</v>
+        <v>0.03350533315393842</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0112607996721737</v>
+        <v>0.03400016596126504</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01154753267517739</v>
+        <v>0.03448868810984104</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0118317133671255</v>
+        <v>0.03497095326860401</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01211335790570707</v>
+        <v>0.03544701471119215</v>
       </c>
       <c r="H3" t="n">
-        <v>0.01239248235882139</v>
+        <v>0.03591692531864685</v>
       </c>
       <c r="I3" t="n">
-        <v>0.01266910270504349</v>
+        <v>0.03638073758209763</v>
       </c>
       <c r="J3" t="n">
-        <v>0.01294323483408736</v>
+        <v>0.03683850360542971</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01321489454726677</v>
+        <v>0.03729027510793367</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0134840975579539</v>
+        <v>0.03773610342693843</v>
       </c>
       <c r="M3" t="n">
-        <v>0.01375085949203568</v>
+        <v>0.03817603952042645</v>
       </c>
       <c r="N3" t="n">
-        <v>0.01401519588836779</v>
+        <v>0.03861013396963224</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0142771221992265</v>
+        <v>0.03903843698162362</v>
       </c>
       <c r="P3" t="n">
-        <v>0.01453665379075819</v>
+        <v>0.03946099839186622</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.01479380594342666</v>
+        <v>0.03987786766677121</v>
       </c>
       <c r="R3" t="n">
-        <v>0.01504859385245826</v>
+        <v>0.04028909390622624</v>
       </c>
       <c r="S3" t="n">
-        <v>0.01530103262828473</v>
+        <v>0.04069472584611</v>
       </c>
       <c r="T3" t="n">
-        <v>0.01555113729698389</v>
+        <v>0.04109481186079007</v>
       </c>
       <c r="U3" t="n">
-        <v>0.01579892280071813</v>
+        <v>0.0414893999656048</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.04187853781932839</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0.04226227272662041</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0.04264065164045885</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0.04301372116455741</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0.04338152755576688</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0.04374411672646084</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.04410153424690568</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0.04445382534761502</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0.04480103492168887</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0.04514320752713721</v>
       </c>
     </row>
   </sheetData>
